--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N77_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N77_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>52.05833655549509</v>
+        <v>8.459479690267953</v>
       </c>
       <c r="D2" t="n">
-        <v>50.17814520529499</v>
+        <v>8.153948595860436</v>
       </c>
       <c r="E2" t="n">
-        <v>16.04021148698653</v>
+        <v>2.606534366635311</v>
       </c>
       <c r="F2" t="n">
-        <v>15.36063886974613</v>
+        <v>2.496103816333746</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>39.72229681511367</v>
+        <v>6.454873232455971</v>
       </c>
       <c r="D3" t="n">
-        <v>26.66940887261119</v>
+        <v>4.333778941799318</v>
       </c>
       <c r="E3" t="n">
-        <v>16.04021148698653</v>
+        <v>2.606534366635311</v>
       </c>
       <c r="F3" t="n">
-        <v>15.36063886974613</v>
+        <v>2.496103816333746</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>13.58452272964615</v>
+        <v>2.2074849435675</v>
       </c>
       <c r="D4" t="n">
-        <v>12.98215747138891</v>
+        <v>2.109600589100698</v>
       </c>
       <c r="E4" t="n">
-        <v>16.04021148698653</v>
+        <v>2.606534366635311</v>
       </c>
       <c r="F4" t="n">
-        <v>15.36063886974613</v>
+        <v>2.496103816333746</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
